--- a/artfynd/A 59481-2025 artfynd.xlsx
+++ b/artfynd/A 59481-2025 artfynd.xlsx
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
@@ -5901,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="AE48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG48" t="b">
         <v>0</v>

--- a/artfynd/A 59481-2025 artfynd.xlsx
+++ b/artfynd/A 59481-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115890990</v>
+        <v>115943620</v>
       </c>
       <c r="B2" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530539</v>
+        <v>530295</v>
       </c>
       <c r="R2" t="n">
-        <v>7235395</v>
+        <v>7236196</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -775,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115891329</v>
+        <v>115891286</v>
       </c>
       <c r="B3" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530520</v>
+        <v>530601</v>
       </c>
       <c r="R3" t="n">
-        <v>7235240</v>
+        <v>7235263</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115891138</v>
+        <v>115943731</v>
       </c>
       <c r="B4" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,7 +925,7 @@
         <v>530422</v>
       </c>
       <c r="R4" t="n">
-        <v>7235319</v>
+        <v>7236139</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,12 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -997,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115891134</v>
+        <v>115943555</v>
       </c>
       <c r="B5" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530421</v>
+        <v>530375</v>
       </c>
       <c r="R5" t="n">
-        <v>7235322</v>
+        <v>7236219</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,12 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1108,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115891278</v>
+        <v>115890952</v>
       </c>
       <c r="B6" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530626</v>
+        <v>530301</v>
       </c>
       <c r="R6" t="n">
-        <v>7235264</v>
+        <v>7235420</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1219,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115891092</v>
+        <v>115891134</v>
       </c>
       <c r="B7" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530391</v>
+        <v>530421</v>
       </c>
       <c r="R7" t="n">
-        <v>7235344</v>
+        <v>7235322</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,12 +1270,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1330,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1341,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115891161</v>
+        <v>115891148</v>
       </c>
       <c r="B8" t="n">
-        <v>104205</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224078</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spenslig fjällnejlika</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viscaria alpina var. serpentinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Rune</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530322</v>
+        <v>530522</v>
       </c>
       <c r="R8" t="n">
-        <v>7235312</v>
+        <v>7235317</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1430,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115891046</v>
+        <v>115943727</v>
       </c>
       <c r="B9" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530311</v>
+        <v>530419</v>
       </c>
       <c r="R9" t="n">
-        <v>7235371</v>
+        <v>7236140</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1541,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1552,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1563,15 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115891030</v>
+        <v>115943868</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,39 +1534,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530374</v>
+        <v>530460</v>
       </c>
       <c r="R10" t="n">
-        <v>7235382</v>
+        <v>7236006</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1638,17 +1588,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,7 +1607,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1673,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1684,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115891126</v>
+        <v>115945060</v>
       </c>
       <c r="B11" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1724,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530579</v>
+        <v>530482</v>
       </c>
       <c r="R11" t="n">
-        <v>7235327</v>
+        <v>7236421</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1754,12 +1694,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1784,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1795,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115891113</v>
+        <v>115945124</v>
       </c>
       <c r="B12" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530419</v>
+        <v>530297</v>
       </c>
       <c r="R12" t="n">
-        <v>7235336</v>
+        <v>7236400</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1865,12 +1800,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,7 +1819,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1895,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1906,15 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115891096</v>
+        <v>115945150</v>
       </c>
       <c r="B13" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1946,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530384</v>
+        <v>530459</v>
       </c>
       <c r="R13" t="n">
-        <v>7235342</v>
+        <v>7236381</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1976,12 +1906,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,7 +1925,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2006,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2017,37 +1947,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115891065</v>
+        <v>115945226</v>
       </c>
       <c r="B14" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530578</v>
+        <v>530378</v>
       </c>
       <c r="R14" t="n">
-        <v>7235355</v>
+        <v>7236351</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2095,11 +2020,6 @@
           <t>2023-09-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Höna stöttes</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2111,7 +2031,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2122,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2133,37 +2053,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115891140</v>
+        <v>115891096</v>
       </c>
       <c r="B15" t="n">
-        <v>90685</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1506</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530536</v>
+        <v>530384</v>
       </c>
       <c r="R15" t="n">
-        <v>7235318</v>
+        <v>7235342</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2203,12 +2118,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,7 +2137,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2244,15 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115891254</v>
+        <v>115891113</v>
       </c>
       <c r="B16" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530605</v>
+        <v>530419</v>
       </c>
       <c r="R16" t="n">
-        <v>7235271</v>
+        <v>7235336</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2314,12 +2224,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,7 +2243,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2355,37 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115891194</v>
+        <v>115891207</v>
       </c>
       <c r="B17" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530479</v>
+        <v>530564</v>
       </c>
       <c r="R17" t="n">
-        <v>7235296</v>
+        <v>7235291</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2444,7 +2349,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2466,15 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115890952</v>
+        <v>115943556</v>
       </c>
       <c r="B18" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,21 +2382,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2506,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530301</v>
+        <v>530375</v>
       </c>
       <c r="R18" t="n">
-        <v>7235420</v>
+        <v>7236218</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2536,12 +2436,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,7 +2455,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2566,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2577,15 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891148</v>
+        <v>115890990</v>
       </c>
       <c r="B19" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,21 +2488,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2617,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530522</v>
+        <v>530539</v>
       </c>
       <c r="R19" t="n">
-        <v>7235317</v>
+        <v>7235395</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2666,7 +2561,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2688,15 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891057</v>
+        <v>115891126</v>
       </c>
       <c r="B20" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1841</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2728,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530382</v>
+        <v>530579</v>
       </c>
       <c r="R20" t="n">
-        <v>7235361</v>
+        <v>7235327</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2758,12 +2648,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2777,7 +2667,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2788,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2799,55 +2689,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891179</v>
+        <v>115891138</v>
       </c>
       <c r="B21" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530534</v>
+        <v>530422</v>
       </c>
       <c r="R21" t="n">
-        <v>7235301</v>
+        <v>7235319</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2874,12 +2754,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2893,7 +2773,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2915,15 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115891286</v>
+        <v>115891254</v>
       </c>
       <c r="B22" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>314</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530601</v>
+        <v>530605</v>
       </c>
       <c r="R22" t="n">
-        <v>7235263</v>
+        <v>7235271</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3004,7 +2879,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3026,15 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891207</v>
+        <v>115891092</v>
       </c>
       <c r="B23" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3042,21 +2912,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530564</v>
+        <v>530391</v>
       </c>
       <c r="R23" t="n">
-        <v>7235291</v>
+        <v>7235344</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3115,7 +2985,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3137,15 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891248</v>
+        <v>115943637</v>
       </c>
       <c r="B24" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3177,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530585</v>
+        <v>530294</v>
       </c>
       <c r="R24" t="n">
-        <v>7235274</v>
+        <v>7236188</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3207,12 +3072,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,7 +3091,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3237,7 +3102,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3248,37 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115943470</v>
+        <v>115891140</v>
       </c>
       <c r="B25" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>1506</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3288,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530387</v>
+        <v>530536</v>
       </c>
       <c r="R25" t="n">
-        <v>7236252</v>
+        <v>7235318</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3318,12 +3178,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3337,7 +3197,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3348,7 +3208,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3359,15 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115943637</v>
+        <v>115891057</v>
       </c>
       <c r="B26" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,21 +3230,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
+        <v>1841</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3399,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530294</v>
+        <v>530382</v>
       </c>
       <c r="R26" t="n">
-        <v>7236188</v>
+        <v>7235361</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3429,12 +3284,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3448,7 +3303,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3470,15 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115943463</v>
+        <v>115943636</v>
       </c>
       <c r="B27" t="n">
-        <v>77446</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3510,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530387</v>
+        <v>530310</v>
       </c>
       <c r="R27" t="n">
-        <v>7236254</v>
+        <v>7236188</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3559,7 +3409,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3570,7 +3420,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3581,15 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115943555</v>
+        <v>115943655</v>
       </c>
       <c r="B28" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3621,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>530375</v>
+        <v>530272</v>
       </c>
       <c r="R28" t="n">
-        <v>7236219</v>
+        <v>7236182</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3670,7 +3515,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3681,7 +3526,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3692,15 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115942698</v>
+        <v>115943647</v>
       </c>
       <c r="B29" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3708,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>4412</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3732,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>530422</v>
+        <v>530425</v>
       </c>
       <c r="R29" t="n">
-        <v>7235470</v>
+        <v>7236186</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3781,7 +3621,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3792,7 +3632,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3803,15 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115943727</v>
+        <v>115945120</v>
       </c>
       <c r="B30" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>4412</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530419</v>
+        <v>530283</v>
       </c>
       <c r="R30" t="n">
-        <v>7236140</v>
+        <v>7236401</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3892,7 +3727,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3914,37 +3749,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115943407</v>
+        <v>115945122</v>
       </c>
       <c r="B31" t="n">
-        <v>77446</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3954,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>530338</v>
+        <v>530273</v>
       </c>
       <c r="R31" t="n">
-        <v>7236283</v>
+        <v>7236401</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3984,12 +3814,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4003,7 +3833,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4025,15 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115943508</v>
+        <v>115943626</v>
       </c>
       <c r="B32" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,34 +3866,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530439</v>
+        <v>530424</v>
       </c>
       <c r="R32" t="n">
-        <v>7236232</v>
+        <v>7236192</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4107,14 +3941,14 @@
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4136,50 +3970,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115943635</v>
+        <v>115943772</v>
       </c>
       <c r="B33" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530309</v>
+        <v>530365</v>
       </c>
       <c r="R33" t="n">
-        <v>7236189</v>
+        <v>7236112</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4206,26 +4044,26 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4236,7 +4074,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4247,37 +4085,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115943556</v>
+        <v>115943337</v>
       </c>
       <c r="B34" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4287,10 +4120,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>530375</v>
+        <v>530370</v>
       </c>
       <c r="R34" t="n">
-        <v>7236218</v>
+        <v>7236314</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4336,7 +4169,7 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4358,37 +4191,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115943641</v>
+        <v>115943747</v>
       </c>
       <c r="B35" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4398,10 +4226,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530421</v>
+        <v>530330</v>
       </c>
       <c r="R35" t="n">
-        <v>7236187</v>
+        <v>7236130</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4447,7 +4275,7 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4469,37 +4297,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115942716</v>
+        <v>115945194</v>
       </c>
       <c r="B36" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4509,10 +4332,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>530438</v>
+        <v>530451</v>
       </c>
       <c r="R36" t="n">
-        <v>7235454</v>
+        <v>7236364</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4539,12 +4362,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4558,7 +4381,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4569,7 +4392,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4580,15 +4403,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115943404</v>
+        <v>115890929</v>
       </c>
       <c r="B37" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4620,10 +4438,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>530338</v>
+        <v>530272</v>
       </c>
       <c r="R37" t="n">
-        <v>7236284</v>
+        <v>7235432</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4650,12 +4468,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4669,7 +4487,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4680,7 +4498,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4691,37 +4509,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115943530</v>
+        <v>115891046</v>
       </c>
       <c r="B38" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4731,10 +4544,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530324</v>
+        <v>530311</v>
       </c>
       <c r="R38" t="n">
-        <v>7236226</v>
+        <v>7235371</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4780,7 +4593,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4791,7 +4604,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4802,15 +4615,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115943642</v>
+        <v>115942684</v>
       </c>
       <c r="B39" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4842,10 +4650,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530421</v>
+        <v>530304</v>
       </c>
       <c r="R39" t="n">
-        <v>7236187</v>
+        <v>7235489</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4891,7 +4699,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4902,7 +4710,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4913,15 +4721,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115943731</v>
+        <v>115942698</v>
       </c>
       <c r="B40" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4929,21 +4732,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4956,7 +4759,7 @@
         <v>530422</v>
       </c>
       <c r="R40" t="n">
-        <v>7236139</v>
+        <v>7235470</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5002,7 +4805,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5013,7 +4816,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5024,37 +4827,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115943649</v>
+        <v>115942716</v>
       </c>
       <c r="B41" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5064,10 +4862,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530326</v>
+        <v>530438</v>
       </c>
       <c r="R41" t="n">
-        <v>7236185</v>
+        <v>7235454</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5094,12 +4892,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5113,7 +4911,7 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5124,7 +4922,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5135,15 +4933,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115943337</v>
+        <v>115943380</v>
       </c>
       <c r="B42" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5151,21 +4944,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5175,10 +4968,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530370</v>
+        <v>530542</v>
       </c>
       <c r="R42" t="n">
-        <v>7236314</v>
+        <v>7236296</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5224,7 +5017,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5235,7 +5028,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5246,15 +5039,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115943626</v>
+        <v>115943399</v>
       </c>
       <c r="B43" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,43 +5050,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530424</v>
+        <v>530551</v>
       </c>
       <c r="R43" t="n">
-        <v>7236192</v>
+        <v>7236288</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5325,26 +5104,26 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5366,15 +5145,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115943620</v>
+        <v>115943404</v>
       </c>
       <c r="B44" t="n">
-        <v>90279</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5382,21 +5156,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>112</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5406,10 +5180,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530295</v>
+        <v>530338</v>
       </c>
       <c r="R44" t="n">
-        <v>7236196</v>
+        <v>7236284</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5455,7 +5229,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5466,7 +5240,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5477,15 +5251,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115943647</v>
+        <v>115943466</v>
       </c>
       <c r="B45" t="n">
-        <v>87189</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5493,21 +5262,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4412</v>
+        <v>6437</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5517,10 +5286,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>530425</v>
+        <v>530386</v>
       </c>
       <c r="R45" t="n">
-        <v>7236186</v>
+        <v>7236253</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5547,12 +5316,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5566,7 +5335,7 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5588,37 +5357,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115943632</v>
+        <v>115943642</v>
       </c>
       <c r="B46" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6437</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5628,10 +5392,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>530308</v>
+        <v>530421</v>
       </c>
       <c r="R46" t="n">
-        <v>7236190</v>
+        <v>7236187</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5658,12 +5422,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5677,7 +5441,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5688,7 +5452,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5699,15 +5463,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115943747</v>
+        <v>115943769</v>
       </c>
       <c r="B47" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5715,21 +5474,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5739,10 +5498,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>530330</v>
+        <v>530451</v>
       </c>
       <c r="R47" t="n">
-        <v>7236130</v>
+        <v>7236114</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5788,7 +5547,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5810,59 +5569,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115943772</v>
+        <v>115891194</v>
       </c>
       <c r="B48" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>530365</v>
+        <v>530479</v>
       </c>
       <c r="R48" t="n">
-        <v>7236112</v>
+        <v>7235296</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5889,26 +5634,26 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5919,7 +5664,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5930,15 +5675,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>115943738</v>
+        <v>115943635</v>
       </c>
       <c r="B49" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5946,21 +5686,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5970,10 +5710,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530428</v>
+        <v>530309</v>
       </c>
       <c r="R49" t="n">
-        <v>7236136</v>
+        <v>7236189</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6000,12 +5740,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6019,7 +5759,7 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6030,7 +5770,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6041,37 +5781,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>115943636</v>
+        <v>115943530</v>
       </c>
       <c r="B50" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6081,10 +5816,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530310</v>
+        <v>530324</v>
       </c>
       <c r="R50" t="n">
-        <v>7236188</v>
+        <v>7236226</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6111,12 +5846,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6130,7 +5865,7 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6141,7 +5876,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6152,37 +5887,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>115942721</v>
+        <v>115943632</v>
       </c>
       <c r="B51" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6192,10 +5922,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530338</v>
+        <v>530308</v>
       </c>
       <c r="R51" t="n">
-        <v>7235449</v>
+        <v>7236190</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6222,12 +5952,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6241,7 +5971,7 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6252,7 +5982,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6263,37 +5993,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>115942684</v>
+        <v>115943649</v>
       </c>
       <c r="B52" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6303,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530304</v>
+        <v>530326</v>
       </c>
       <c r="R52" t="n">
-        <v>7235489</v>
+        <v>7236185</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6333,12 +6058,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6352,7 +6077,7 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6363,7 +6088,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6374,37 +6099,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>115943408</v>
+        <v>115943738</v>
       </c>
       <c r="B53" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6414,10 +6134,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530337</v>
+        <v>530428</v>
       </c>
       <c r="R53" t="n">
-        <v>7236283</v>
+        <v>7236136</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6444,12 +6164,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6463,7 +6183,7 @@
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6485,15 +6205,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>115942703</v>
+        <v>115943407</v>
       </c>
       <c r="B54" t="n">
-        <v>104205</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6501,21 +6216,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>224078</v>
+        <v>6487</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spenslig fjällnejlika</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Viscaria alpina var. serpentinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Rune</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6525,10 +6240,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>530393</v>
+        <v>530338</v>
       </c>
       <c r="R54" t="n">
-        <v>7235463</v>
+        <v>7236283</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6555,12 +6270,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6574,7 +6289,7 @@
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6585,7 +6300,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6596,15 +6311,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>115943466</v>
+        <v>115943463</v>
       </c>
       <c r="B55" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6612,21 +6322,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6636,10 +6346,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>530386</v>
+        <v>530387</v>
       </c>
       <c r="R55" t="n">
-        <v>7236253</v>
+        <v>7236254</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6685,7 +6395,7 @@
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6707,15 +6417,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>115945060</v>
+        <v>115891030</v>
       </c>
       <c r="B56" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6723,34 +6428,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>530482</v>
+        <v>530374</v>
       </c>
       <c r="R56" t="n">
-        <v>7236421</v>
+        <v>7235382</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6777,12 +6487,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6796,7 +6511,7 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6818,15 +6533,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>115945150</v>
+        <v>127682199</v>
       </c>
       <c r="B57" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6834,37 +6544,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Bergsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>530459</v>
+        <v>530657</v>
       </c>
       <c r="R57" t="n">
-        <v>7236381</v>
+        <v>7235099</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6888,12 +6603,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6904,62 +6629,48 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>5169</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>115945124</v>
+        <v>115891065</v>
       </c>
       <c r="B58" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6969,10 +6680,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530297</v>
+        <v>530578</v>
       </c>
       <c r="R58" t="n">
-        <v>7236400</v>
+        <v>7235355</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7007,6 +6718,11 @@
           <t>2023-09-17</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Höna stöttes</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7018,7 +6734,7 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7029,7 +6745,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7040,15 +6756,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>115945263</v>
+        <v>115942721</v>
       </c>
       <c r="B59" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7056,21 +6767,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7080,10 +6791,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>530385</v>
+        <v>530338</v>
       </c>
       <c r="R59" t="n">
-        <v>7236340</v>
+        <v>7235449</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7129,7 +6840,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7140,7 +6851,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7151,15 +6862,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>115945226</v>
+        <v>115943508</v>
       </c>
       <c r="B60" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7167,21 +6873,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7191,10 +6897,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>530378</v>
+        <v>530439</v>
       </c>
       <c r="R60" t="n">
-        <v>7236351</v>
+        <v>7236232</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7240,7 +6946,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7262,15 +6968,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>115945194</v>
+        <v>115942905</v>
       </c>
       <c r="B61" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7278,21 +6979,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7302,10 +7003,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>530451</v>
+        <v>530458</v>
       </c>
       <c r="R61" t="n">
-        <v>7236364</v>
+        <v>7235960</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7332,12 +7033,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7351,7 +7052,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7362,10 +7063,1313 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>115943383</v>
+      </c>
+      <c r="B62" t="n">
+        <v>29424</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>103271</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tajgahumla</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bombus cingulatus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Wahlberg, 1855</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>530330</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7236294</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>5626</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>115891179</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>530534</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7235301</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>7963</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Julia Falk</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>115945017</v>
+      </c>
+      <c r="B64" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>530492</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7236445</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>5152</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>115945026</v>
+      </c>
+      <c r="B65" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>530505</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7236442</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>115891161</v>
+      </c>
+      <c r="B66" t="n">
+        <v>105706</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224078</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spenslig fjällnejlika</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Viscaria alpina var. serpentinicola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Rune</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>530322</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7235312</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>7876</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Julia Falk</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>115942703</v>
+      </c>
+      <c r="B67" t="n">
+        <v>105706</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>224078</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spenslig fjällnejlika</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Viscaria alpina var. serpentinicola</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Rune</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>530393</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7235463</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Julia Falk</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>115943381</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>530540</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7236296</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>5638</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>115943398</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>530551</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7236288</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>5640</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>115943408</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>530337</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7236283</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>5618</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>115943470</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>530387</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7236252</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>5615</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>115943641</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>530421</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7236187</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>7894</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>115945087</v>
+      </c>
+      <c r="B73" t="n">
+        <v>95765</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>530570</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7236409</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>5179</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
